--- a/tests/vlaanderen/reference/resultaten/werk/concurrentie/arbeidsplaatsen/restdag/Ontpl_conc_Auto_OV.xlsx
+++ b/tests/vlaanderen/reference/resultaten/werk/concurrentie/arbeidsplaatsen/restdag/Ontpl_conc_Auto_OV.xlsx
@@ -385,16 +385,16 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>0.5582697136662433</v>
+        <v>0.4931821122603382</v>
       </c>
       <c r="C2">
-        <v>0.7020990846397795</v>
+        <v>0.661573293841316</v>
       </c>
       <c r="D2">
-        <v>0.7536277294702586</v>
+        <v>0.7290632462805418</v>
       </c>
       <c r="E2">
-        <v>0.7747833279462306</v>
+        <v>0.7685891331095891</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -402,16 +402,16 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>0.5655495099421098</v>
+        <v>0.5153633397146761</v>
       </c>
       <c r="C3">
-        <v>0.7079339602863506</v>
+        <v>0.6738667883227225</v>
       </c>
       <c r="D3">
-        <v>0.7570069272544382</v>
+        <v>0.7333613288730276</v>
       </c>
       <c r="E3">
-        <v>0.7770276209792533</v>
+        <v>0.7708789861869617</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -419,16 +419,16 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>0.5016439196761076</v>
+        <v>0.4374902955487354</v>
       </c>
       <c r="C4">
-        <v>0.6671393909086752</v>
+        <v>0.6187979655781662</v>
       </c>
       <c r="D4">
-        <v>0.7349999972699376</v>
+        <v>0.7046267294810441</v>
       </c>
       <c r="E4">
-        <v>0.7582039047428399</v>
+        <v>0.7464637078808254</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -436,16 +436,16 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>0.5676563923828505</v>
+        <v>0.5298897655057369</v>
       </c>
       <c r="C5">
-        <v>0.7116557279080611</v>
+        <v>0.6897892064502114</v>
       </c>
       <c r="D5">
-        <v>0.7577576192567733</v>
+        <v>0.7380320129858585</v>
       </c>
       <c r="E5">
-        <v>0.7817840426466831</v>
+        <v>0.7764259826412993</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -453,16 +453,16 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>0.5388075863301401</v>
+        <v>0.5057688546224985</v>
       </c>
       <c r="C6">
-        <v>0.6921269154972672</v>
+        <v>0.6652366117247697</v>
       </c>
       <c r="D6">
-        <v>0.7497759552333861</v>
+        <v>0.7291236296109174</v>
       </c>
       <c r="E6">
-        <v>0.7760571709281976</v>
+        <v>0.7706515248517226</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -470,16 +470,16 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>0.5982250303273913</v>
+        <v>0.5447578938268327</v>
       </c>
       <c r="C7">
-        <v>0.7311301017741306</v>
+        <v>0.6933145588868495</v>
       </c>
       <c r="D7">
-        <v>0.7729662477052786</v>
+        <v>0.7506844926718718</v>
       </c>
       <c r="E7">
-        <v>0.7826180338824664</v>
+        <v>0.7806982292143918</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -487,16 +487,16 @@
         <v>7</v>
       </c>
       <c r="B8">
-        <v>0.2714089355384538</v>
+        <v>0.3387555889314413</v>
       </c>
       <c r="C8">
-        <v>0.4825273335458954</v>
+        <v>0.5333783912550941</v>
       </c>
       <c r="D8">
-        <v>0.6135086850507573</v>
+        <v>0.6524168076416768</v>
       </c>
       <c r="E8">
-        <v>0.71399605079497</v>
+        <v>0.7251023143756458</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -504,16 +504,16 @@
         <v>8</v>
       </c>
       <c r="B9">
-        <v>0.5289994715570385</v>
+        <v>0.5507354905628262</v>
       </c>
       <c r="C9">
-        <v>0.6760054899001348</v>
+        <v>0.6843487676573281</v>
       </c>
       <c r="D9">
-        <v>0.7399637731815616</v>
+        <v>0.7300219831045288</v>
       </c>
       <c r="E9">
-        <v>0.763268773452269</v>
+        <v>0.7631747969005328</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -521,16 +521,16 @@
         <v>9</v>
       </c>
       <c r="B10">
-        <v>0.6289567929654097</v>
+        <v>0.5757433387719072</v>
       </c>
       <c r="C10">
-        <v>0.7598594951260311</v>
+        <v>0.7168369832582071</v>
       </c>
       <c r="D10">
-        <v>0.7888481291569622</v>
+        <v>0.7604444292657107</v>
       </c>
       <c r="E10">
-        <v>0.7998265137805515</v>
+        <v>0.7899586053769507</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -538,16 +538,16 @@
         <v>10</v>
       </c>
       <c r="B11">
-        <v>0.6226942439590685</v>
+        <v>0.5695263211412293</v>
       </c>
       <c r="C11">
-        <v>0.7556771256224231</v>
+        <v>0.7094089328744574</v>
       </c>
       <c r="D11">
-        <v>0.7865039493820257</v>
+        <v>0.7567833805556493</v>
       </c>
       <c r="E11">
-        <v>0.7979297844464777</v>
+        <v>0.7877220119822033</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -555,16 +555,16 @@
         <v>11</v>
       </c>
       <c r="B12">
-        <v>0.5745126601619753</v>
+        <v>0.5945354592179901</v>
       </c>
       <c r="C12">
-        <v>0.7231763437576213</v>
+        <v>0.7037786893688498</v>
       </c>
       <c r="D12">
-        <v>0.7717791700251481</v>
+        <v>0.7454720414069178</v>
       </c>
       <c r="E12">
-        <v>0.7826881838904574</v>
+        <v>0.7733773858512553</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -572,16 +572,16 @@
         <v>12</v>
       </c>
       <c r="B13">
-        <v>0.6127564029467489</v>
+        <v>0.5618534312278398</v>
       </c>
       <c r="C13">
-        <v>0.7490676502734643</v>
+        <v>0.7043203983323243</v>
       </c>
       <c r="D13">
-        <v>0.7830607682763813</v>
+        <v>0.754178808815176</v>
       </c>
       <c r="E13">
-        <v>0.7951664937103869</v>
+        <v>0.7852402058903404</v>
       </c>
     </row>
   </sheetData>

--- a/tests/vlaanderen/reference/resultaten/werk/concurrentie/arbeidsplaatsen/restdag/Ontpl_conc_Auto_OV.xlsx
+++ b/tests/vlaanderen/reference/resultaten/werk/concurrentie/arbeidsplaatsen/restdag/Ontpl_conc_Auto_OV.xlsx
@@ -385,16 +385,16 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>0.4931821122603382</v>
+        <v>1.66648302963179</v>
       </c>
       <c r="C2">
-        <v>0.661573293841316</v>
+        <v>1.051992419062077</v>
       </c>
       <c r="D2">
-        <v>0.7290632462805418</v>
+        <v>0.5972206712046595</v>
       </c>
       <c r="E2">
-        <v>0.7685891331095891</v>
+        <v>0.4135469769143428</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -402,16 +402,16 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>0.5153633397146761</v>
+        <v>0.9768824618418059</v>
       </c>
       <c r="C3">
-        <v>0.6738667883227225</v>
+        <v>0.6918980882514457</v>
       </c>
       <c r="D3">
-        <v>0.7333613288730276</v>
+        <v>0.6195021608105384</v>
       </c>
       <c r="E3">
-        <v>0.7708789861869617</v>
+        <v>0.5868728412152472</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -419,16 +419,16 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>0.4374902955487354</v>
+        <v>1.067169310405196</v>
       </c>
       <c r="C4">
-        <v>0.6187979655781662</v>
+        <v>0.8024832564129485</v>
       </c>
       <c r="D4">
-        <v>0.7046267294810441</v>
+        <v>0.5729315816786221</v>
       </c>
       <c r="E4">
-        <v>0.7464637078808254</v>
+        <v>0.4701935608377747</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -436,16 +436,16 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>0.5298897655057369</v>
+        <v>0.1320623099789839</v>
       </c>
       <c r="C5">
-        <v>0.6897892064502114</v>
+        <v>0.1729811941872047</v>
       </c>
       <c r="D5">
-        <v>0.7380320129858585</v>
+        <v>0.1839367710382712</v>
       </c>
       <c r="E5">
-        <v>0.7764259826412993</v>
+        <v>0.1947074445632979</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -453,16 +453,16 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>0.5057688546224985</v>
+        <v>0.5567923106583715</v>
       </c>
       <c r="C6">
-        <v>0.6652366117247697</v>
+        <v>0.5762735576231368</v>
       </c>
       <c r="D6">
-        <v>0.7291236296109174</v>
+        <v>0.6880112358096764</v>
       </c>
       <c r="E6">
-        <v>0.7706515248517226</v>
+        <v>0.8790931617911869</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -470,16 +470,16 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>0.5447578938268327</v>
+        <v>1.035039998270982</v>
       </c>
       <c r="C7">
-        <v>0.6933145588868495</v>
+        <v>0.658648830942507</v>
       </c>
       <c r="D7">
-        <v>0.7506844926718718</v>
+        <v>0.6483184254893437</v>
       </c>
       <c r="E7">
-        <v>0.7806982292143918</v>
+        <v>0.618052764794727</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -487,16 +487,16 @@
         <v>7</v>
       </c>
       <c r="B8">
-        <v>0.3387555889314413</v>
+        <v>0.08466317937764234</v>
       </c>
       <c r="C8">
-        <v>0.5333783912550941</v>
+        <v>0.1334660778603697</v>
       </c>
       <c r="D8">
-        <v>0.6524168076416768</v>
+        <v>0.1630546713298208</v>
       </c>
       <c r="E8">
-        <v>0.7251023143756458</v>
+        <v>0.1812205298302935</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -504,16 +504,16 @@
         <v>8</v>
       </c>
       <c r="B9">
-        <v>0.5507354905628262</v>
+        <v>1.022704381124013</v>
       </c>
       <c r="C9">
-        <v>0.6843487676573281</v>
+        <v>0.7967731626103152</v>
       </c>
       <c r="D9">
-        <v>0.7300219831045288</v>
+        <v>0.6254179564275042</v>
       </c>
       <c r="E9">
-        <v>0.7631747969005328</v>
+        <v>0.5322316861721581</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -521,16 +521,16 @@
         <v>9</v>
       </c>
       <c r="B10">
-        <v>0.5757433387719072</v>
+        <v>0.1447678337374449</v>
       </c>
       <c r="C10">
-        <v>0.7168369832582071</v>
+        <v>0.178173354220248</v>
       </c>
       <c r="D10">
-        <v>0.7604444292657107</v>
+        <v>0.1912100154512048</v>
       </c>
       <c r="E10">
-        <v>0.7899586053769507</v>
+        <v>0.1963480926659473</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -538,16 +538,16 @@
         <v>10</v>
       </c>
       <c r="B11">
-        <v>0.5695263211412293</v>
+        <v>0.1469745344880592</v>
       </c>
       <c r="C11">
-        <v>0.7094089328744574</v>
+        <v>0.1716311934373687</v>
       </c>
       <c r="D11">
-        <v>0.7567833805556493</v>
+        <v>0.1830927533602378</v>
       </c>
       <c r="E11">
-        <v>0.7877220119822033</v>
+        <v>0.203283099866375</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -555,16 +555,16 @@
         <v>11</v>
       </c>
       <c r="B12">
-        <v>0.5945354592179901</v>
+        <v>0.5530023473434954</v>
       </c>
       <c r="C12">
-        <v>0.7037786893688498</v>
+        <v>0.6022474443231282</v>
       </c>
       <c r="D12">
-        <v>0.7454720414069178</v>
+        <v>0.7536557828718982</v>
       </c>
       <c r="E12">
-        <v>0.7733773858512553</v>
+        <v>1.013438218112418</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -572,16 +572,16 @@
         <v>12</v>
       </c>
       <c r="B13">
-        <v>0.5618534312278398</v>
+        <v>0.1411836827187905</v>
       </c>
       <c r="C13">
-        <v>0.7043203983323243</v>
+        <v>0.1733711749741106</v>
       </c>
       <c r="D13">
-        <v>0.754178808815176</v>
+        <v>0.1895115981125314</v>
       </c>
       <c r="E13">
-        <v>0.7852402058903404</v>
+        <v>0.1973167696852651</v>
       </c>
     </row>
   </sheetData>
